--- a/Convert_from_xlsx_to_Json/table_normalization/education-table31.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table31.xlsx
@@ -144,7 +144,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,12 +154,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,7 +209,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -228,9 +222,7 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal_Sheet1" xfId="1"/>
@@ -775,7 +767,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -825,7 +817,7 @@
       <c r="O2" s="3">
         <v>4</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="2">
         <f t="shared" ref="T2:T16" si="0">SUM(D2:S2)</f>
         <v>25</v>
       </c>
@@ -876,7 +868,7 @@
       <c r="O3" s="3">
         <v>2</v>
       </c>
-      <c r="T3" s="7">
+      <c r="T3" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -927,7 +919,7 @@
       <c r="O4" s="3">
         <v>2</v>
       </c>
-      <c r="T4" s="7">
+      <c r="T4" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -942,7 +934,6 @@
       <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T5" s="7"/>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2">
@@ -994,7 +985,7 @@
       <c r="S6" s="3">
         <v>2</v>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1049,7 +1040,7 @@
       <c r="S7" s="4">
         <v>2</v>
       </c>
-      <c r="T7" s="7">
+      <c r="T7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1104,7 +1095,7 @@
       <c r="S8" s="3">
         <v>1</v>
       </c>
-      <c r="T8" s="7">
+      <c r="T8" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1159,7 +1150,7 @@
       <c r="S9" s="3">
         <v>2</v>
       </c>
-      <c r="T9" s="7">
+      <c r="T9" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1210,7 +1201,7 @@
       <c r="O10" s="3">
         <v>3</v>
       </c>
-      <c r="T10" s="7">
+      <c r="T10" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -1261,7 +1252,7 @@
       <c r="O11" s="3">
         <v>2</v>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -1312,7 +1303,7 @@
       <c r="O12" s="3">
         <v>4</v>
       </c>
-      <c r="T12" s="7">
+      <c r="T12" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1363,7 +1354,7 @@
       <c r="O13" s="3">
         <v>2</v>
       </c>
-      <c r="T13" s="7">
+      <c r="T13" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1414,7 +1405,7 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="7">
+      <c r="T14" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1465,7 +1456,7 @@
       <c r="O15" s="3">
         <v>3</v>
       </c>
-      <c r="T15" s="7">
+      <c r="T15" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -1516,7 +1507,7 @@
       <c r="O16" s="3">
         <v>3</v>
       </c>
-      <c r="T16" s="7">
+      <c r="T16" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -1531,7 +1522,7 @@
       <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T17" s="7">
+      <c r="T17" s="2">
         <v>23</v>
       </c>
     </row>
@@ -1581,7 +1572,7 @@
       <c r="O18" s="3">
         <v>4</v>
       </c>
-      <c r="T18" s="7">
+      <c r="T18" s="2">
         <f t="shared" ref="T18:T20" si="1">SUM(D18:S18)</f>
         <v>30</v>
       </c>
@@ -1632,7 +1623,7 @@
       <c r="O19" s="3">
         <v>3</v>
       </c>
-      <c r="T19" s="7">
+      <c r="T19" s="2">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
@@ -1683,7 +1674,7 @@
       <c r="O20" s="3">
         <v>1</v>
       </c>
-      <c r="T20" s="7">
+      <c r="T20" s="2">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
@@ -1698,7 +1689,7 @@
       <c r="C21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T21" s="7">
+      <c r="T21" s="2">
         <v>20</v>
       </c>
     </row>
@@ -1752,7 +1743,7 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="7">
+      <c r="T22" s="2">
         <f t="shared" ref="T22:T25" si="2">SUM(D22:S22)</f>
         <v>2</v>
       </c>
@@ -1803,7 +1794,7 @@
       <c r="O23" s="3">
         <v>2</v>
       </c>
-      <c r="T23" s="7">
+      <c r="T23" s="2">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
@@ -1834,7 +1825,6 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
-      <c r="T24" s="7"/>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="2">
@@ -1882,7 +1872,7 @@
       <c r="O25" s="3">
         <v>2</v>
       </c>
-      <c r="T25" s="7">
+      <c r="T25" s="2">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
@@ -1897,7 +1887,6 @@
       <c r="C26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T26" s="7"/>
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="2">
@@ -1949,7 +1938,7 @@
       <c r="S27" s="4">
         <v>-1</v>
       </c>
-      <c r="T27" s="7">
+      <c r="T27" s="2">
         <f t="shared" ref="T27:T36" si="3">SUM(D27:S27)</f>
         <v>8</v>
       </c>
@@ -1964,7 +1953,6 @@
       <c r="C28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T28" s="7"/>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="2">
@@ -2012,7 +2000,7 @@
       <c r="O29" s="3">
         <v>4</v>
       </c>
-      <c r="T29" s="7">
+      <c r="T29" s="2">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -2063,7 +2051,7 @@
       <c r="O30" s="3">
         <v>2</v>
       </c>
-      <c r="T30" s="7">
+      <c r="T30" s="2">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
@@ -2114,7 +2102,7 @@
       <c r="O31" s="3">
         <v>2</v>
       </c>
-      <c r="T31" s="7">
+      <c r="T31" s="2">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
@@ -2165,7 +2153,7 @@
       <c r="O32" s="3">
         <v>2</v>
       </c>
-      <c r="T32" s="7">
+      <c r="T32" s="2">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -2220,7 +2208,7 @@
       <c r="S33" s="3">
         <v>4</v>
       </c>
-      <c r="T33" s="7">
+      <c r="T33" s="2">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
@@ -2271,7 +2259,7 @@
       <c r="O34" s="3">
         <v>2</v>
       </c>
-      <c r="T34" s="7">
+      <c r="T34" s="2">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
@@ -2326,7 +2314,7 @@
       <c r="S35" s="3">
         <v>2</v>
       </c>
-      <c r="T35" s="7">
+      <c r="T35" s="2">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
@@ -2377,7 +2365,7 @@
       <c r="O36" s="3">
         <v>2</v>
       </c>
-      <c r="T36" s="7">
+      <c r="T36" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
@@ -2392,7 +2380,6 @@
       <c r="C37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T37" s="7"/>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="2">
@@ -2444,7 +2431,7 @@
       <c r="S38" s="3">
         <v>0</v>
       </c>
-      <c r="T38" s="7">
+      <c r="T38" s="2">
         <f>SUM(D38:S38)</f>
         <v>3</v>
       </c>
@@ -2459,7 +2446,6 @@
       <c r="C39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T39" s="7"/>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="2">
@@ -2507,7 +2493,7 @@
       <c r="O40" s="3">
         <v>2</v>
       </c>
-      <c r="T40" s="7">
+      <c r="T40" s="2">
         <f>SUM(D40:S40)</f>
         <v>16</v>
       </c>
@@ -2522,7 +2508,6 @@
       <c r="C41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T41" s="7"/>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="2">
@@ -2534,10 +2519,9 @@
       <c r="C42" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T42" s="7"/>
     </row>
     <row r="43" spans="1:20">
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="2">
@@ -2606,7 +2590,7 @@
       </c>
     </row>
     <row r="44" spans="1:20">
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="2">
@@ -2675,7 +2659,7 @@
       </c>
     </row>
     <row r="45" spans="1:20">
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="2">
